--- a/data/planning/overload.xlsx
+++ b/data/planning/overload.xlsx
@@ -3243,50 +3243,85 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>work_type_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>received_at</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sla_deadline_at</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>required_transport_type</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>service_duration_source</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>visit_window_start</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>visit_window_end</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>planned_start_at</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>planned_end_at</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>estimated_duration_minutes</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>actual_duration_minutes</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -3316,50 +3351,85 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3389,50 +3459,85 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3462,50 +3567,85 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -3535,50 +3675,85 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3608,50 +3783,85 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3681,50 +3891,85 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -3754,50 +3999,85 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -3827,50 +4107,85 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3900,50 +4215,85 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -3973,50 +4323,85 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -4046,50 +4431,85 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -4119,50 +4539,85 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -4192,50 +4647,85 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -4265,50 +4755,85 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -4338,50 +4863,85 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -4411,50 +4971,85 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -4484,50 +5079,85 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -4557,50 +5187,85 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -4630,50 +5295,85 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -4703,50 +5403,85 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -4776,50 +5511,85 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -4849,50 +5619,85 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -4922,50 +5727,85 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -4995,50 +5835,85 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -5068,50 +5943,85 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -5141,50 +6051,85 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -5214,50 +6159,85 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -5287,50 +6267,85 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -5360,50 +6375,85 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
         <is>
           <t>29</t>
         </is>
@@ -5433,50 +6483,85 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -5506,50 +6591,85 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
         <is>
           <t>31</t>
         </is>
@@ -5579,50 +6699,85 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
         <is>
           <t>32</t>
         </is>
@@ -5652,50 +6807,85 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
         <is>
           <t>33</t>
         </is>
@@ -5725,50 +6915,85 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -5798,50 +7023,85 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -5871,50 +7131,85 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -5944,50 +7239,85 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -6017,50 +7347,85 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -6090,50 +7455,85 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
         <is>
           <t>39</t>
         </is>
@@ -6163,50 +7563,85 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -6236,50 +7671,85 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
         <is>
           <t>41</t>
         </is>
@@ -6309,50 +7779,85 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
         <is>
           <t>42</t>
         </is>
@@ -6382,50 +7887,85 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
         <is>
           <t>43</t>
         </is>
@@ -6455,50 +7995,85 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
         <is>
           <t>44</t>
         </is>
@@ -6528,50 +8103,85 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
         <is>
           <t>45</t>
         </is>
@@ -6601,50 +8211,85 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
         <is>
           <t>46</t>
         </is>
@@ -6674,50 +8319,85 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
         <is>
           <t>47</t>
         </is>
@@ -6747,50 +8427,85 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -6820,50 +8535,85 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
         <is>
           <t>49</t>
         </is>
@@ -6893,50 +8643,85 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -14261,25 +16046,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>default_priority</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>travel_minutes</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>work_minutes</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>documents_minutes</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>norm_minutes</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -14293,25 +16093,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>synthetic_1900_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -14325,25 +16140,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>synthetic_1900_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -14357,25 +16187,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>synthetic_1900_3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>3</t>
         </is>

--- a/data/planning/overload.xlsx
+++ b/data/planning/overload.xlsx
@@ -3572,85 +3572,120 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>work_type_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>received_at</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sla_deadline_at</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>required_transport_type</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>service_duration_source</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>lifecycle_state</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>visit_window_start</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>visit_window_end</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>planned_start_at</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>planned_end_at</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>estimated_duration_minutes</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>actual_duration_minutes</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>revision</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>execution_cycle</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>actual_started_at</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>actual_completed_at</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>cancel_reason</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>last_event_id</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -3680,85 +3715,120 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3788,85 +3858,120 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3896,85 +4001,120 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -4004,85 +4144,120 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -4112,85 +4287,120 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -4220,85 +4430,120 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -4328,85 +4573,120 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -4436,85 +4716,120 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -4544,85 +4859,120 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -4652,85 +5002,120 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -4760,85 +5145,120 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -4868,85 +5288,120 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -4976,85 +5431,120 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -5084,85 +5574,120 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -5192,85 +5717,120 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -5300,85 +5860,120 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -5408,85 +6003,120 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -5516,85 +6146,120 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -5624,85 +6289,120 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -5732,85 +6432,120 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -5840,85 +6575,120 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -5948,85 +6718,120 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -6056,85 +6861,120 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -6164,85 +7004,120 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -6272,85 +7147,120 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -6380,85 +7290,120 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -6488,85 +7433,120 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -6596,85 +7576,120 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -6704,85 +7719,120 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
         <is>
           <t>29</t>
         </is>
@@ -6812,85 +7862,120 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -6920,85 +8005,120 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
         <is>
           <t>31</t>
         </is>
@@ -7028,85 +8148,120 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
         <is>
           <t>32</t>
         </is>
@@ -7136,85 +8291,120 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
         <is>
           <t>33</t>
         </is>
@@ -7244,85 +8434,120 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -7352,85 +8577,120 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -7460,85 +8720,120 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -7568,85 +8863,120 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -7676,85 +9006,120 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -7784,85 +9149,120 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
         <is>
           <t>39</t>
         </is>
@@ -7892,85 +9292,120 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -8000,85 +9435,120 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
         <is>
           <t>41</t>
         </is>
@@ -8108,85 +9578,120 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
         <is>
           <t>42</t>
         </is>
@@ -8216,85 +9721,120 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
         <is>
           <t>43</t>
         </is>
@@ -8324,85 +9864,120 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
         <is>
           <t>44</t>
         </is>
@@ -8432,85 +10007,120 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
         <is>
           <t>45</t>
         </is>
@@ -8540,85 +10150,120 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
         <is>
           <t>46</t>
         </is>
@@ -8648,85 +10293,120 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
         <is>
           <t>47</t>
         </is>
@@ -8756,85 +10436,120 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -8864,85 +10579,120 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
         <is>
           <t>49</t>
         </is>
@@ -8972,85 +10722,120 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2030-01-15T07:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ticket_estimate</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t>planned</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>waiting_assignment</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
         <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -17008,25 +18793,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>default_priority</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>travel_minutes</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>work_minutes</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>documents_minutes</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>norm_minutes</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -17040,25 +18840,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>synthetic_1900_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -17072,25 +18887,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>synthetic_1900_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -17104,25 +18934,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>synthetic_1900_3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>repair</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>3</t>
         </is>

--- a/data/planning/overload.xlsx
+++ b/data/planning/overload.xlsx
@@ -30,14 +30,13 @@
     <sheet name="brigades" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="notification_events" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="ticket_appliances" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="ticket_assignments" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="ticket_comments" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="work_events" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="worker_day_states" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="brigade_members" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="day_plan_revisions" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="equipment_movements" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="routes" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="ticket_comments" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="work_events" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="worker_day_states" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="brigade_members" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="day_plan_revisions" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="equipment_movements" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="routes" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3617,75 +3616,85 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>assigned_worker_id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>is_pinned</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>visit_window_start</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>visit_window_end</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>planned_start_at</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>planned_end_at</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>estimated_duration_minutes</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>actual_duration_minutes</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>revision</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>execution_cycle</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>actual_started_at</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>actual_completed_at</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>cancel_reason</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>last_event_id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -3760,52 +3769,52 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -3820,15 +3829,25 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3903,52 +3922,52 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -3963,15 +3982,25 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -4046,52 +4075,52 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -4106,15 +4135,25 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -4189,52 +4228,52 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -4249,15 +4288,25 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -4332,52 +4381,52 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -4392,15 +4441,25 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -4475,52 +4534,52 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -4535,15 +4594,25 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -4618,52 +4687,52 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -4678,15 +4747,25 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -4761,52 +4840,52 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4821,15 +4900,25 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -4904,52 +4993,52 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4964,15 +5053,25 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -5047,52 +5146,52 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5107,15 +5206,25 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -5190,52 +5299,52 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R12" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5250,15 +5359,25 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -5333,52 +5452,52 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5393,15 +5512,25 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -5476,52 +5605,52 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -5536,15 +5665,25 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -5619,52 +5758,52 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R15" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -5679,15 +5818,25 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -5762,52 +5911,52 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R16" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -5822,15 +5971,25 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -5905,52 +6064,52 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R17" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -5965,15 +6124,25 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -6048,52 +6217,52 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R18" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -6108,15 +6277,25 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -6191,52 +6370,52 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R19" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -6251,15 +6430,25 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -6334,52 +6523,52 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R20" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -6394,15 +6583,25 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -6477,52 +6676,52 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R21" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -6537,15 +6736,25 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -6620,52 +6829,52 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R22" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -6680,15 +6889,25 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -6763,52 +6982,52 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R23" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -6823,15 +7042,25 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -6906,52 +7135,52 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R24" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -6966,15 +7195,25 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -7049,52 +7288,52 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R25" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -7109,15 +7348,25 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -7192,52 +7441,52 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R26" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -7252,15 +7501,25 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -7335,52 +7594,52 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R27" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -7395,15 +7654,25 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -7478,52 +7747,52 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R28" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -7538,15 +7807,25 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -7621,52 +7900,52 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R29" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -7681,15 +7960,25 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -7764,52 +8053,52 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R30" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -7824,15 +8113,25 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
         <is>
           <t>29</t>
         </is>
@@ -7907,52 +8206,52 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R31" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -7967,15 +8266,25 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -8050,52 +8359,52 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R32" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -8110,15 +8419,25 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
         <is>
           <t>31</t>
         </is>
@@ -8193,52 +8512,52 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R33" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -8253,15 +8572,25 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
         <is>
           <t>32</t>
         </is>
@@ -8336,52 +8665,52 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R34" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -8396,15 +8725,25 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
         <is>
           <t>33</t>
         </is>
@@ -8479,52 +8818,52 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R35" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -8539,15 +8878,25 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -8622,52 +8971,52 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R36" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -8682,15 +9031,25 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -8765,52 +9124,52 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R37" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -8825,15 +9184,25 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -8908,52 +9277,52 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R38" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -8968,15 +9337,25 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -9051,52 +9430,52 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R39" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -9111,15 +9490,25 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -9194,52 +9583,52 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R40" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -9254,15 +9643,25 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
         <is>
           <t>39</t>
         </is>
@@ -9337,52 +9736,52 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R41" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -9397,15 +9796,25 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -9480,52 +9889,52 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R42" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -9540,15 +9949,25 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
         <is>
           <t>41</t>
         </is>
@@ -9623,52 +10042,52 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R43" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -9683,15 +10102,25 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
         <is>
           <t>42</t>
         </is>
@@ -9766,52 +10195,52 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R44" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -9826,15 +10255,25 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
         <is>
           <t>43</t>
         </is>
@@ -9909,52 +10348,52 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R45" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -9969,15 +10408,25 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
         <is>
           <t>44</t>
         </is>
@@ -10052,52 +10501,52 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R46" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -10112,15 +10561,25 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
         <is>
           <t>45</t>
         </is>
@@ -10195,52 +10654,52 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R47" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -10255,15 +10714,25 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
         <is>
           <t>46</t>
         </is>
@@ -10338,52 +10807,52 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R48" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -10398,15 +10867,25 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
         <is>
           <t>47</t>
         </is>
@@ -10481,52 +10960,52 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R49" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -10541,15 +11020,25 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -10624,52 +11113,52 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R50" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -10684,15 +11173,25 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
         <is>
           <t>49</t>
         </is>
@@ -10767,52 +11266,52 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
           <t>2030-01-15T18:00:00+03:00</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
       <c r="R51" t="inlineStr">
         <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -10827,15 +11326,25 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -17382,12 +17891,27 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>worker_id</t>
+          <t>author_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>assigned_at</t>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>id</t>
         </is>
       </c>
     </row>
@@ -17407,32 +17931,164 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>event_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>ticket_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>author_id</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>worker_id</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>district_id</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>route_date</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>occurred_at</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>recorded_at</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>actor_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>previous_state</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>new_state</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>before_revision</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>after_revision</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>idempotency_key</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>payload</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>new_ticket</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2030-01-15</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>waiting_assignment</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>synthetic-1900-ticket-1</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>{"ticket_id":1}</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -17452,77 +18108,77 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>event_type</t>
+          <t>worker_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>ticket_id</t>
+          <t>district_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>worker_id</t>
+          <t>route_date</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>district_id</t>
+          <t>revision</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>route_date</t>
+          <t>available</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>occurred_at</t>
+          <t>unavailable_at</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>recorded_at</t>
+          <t>unavailable_until</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>actor_id</t>
+          <t>last_location_id</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>current_ticket_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>current_destination_id</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>en_route_started_at</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>expected_available_at</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>previous_state</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>new_state</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>before_revision</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>after_revision</t>
-        </is>
-      </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>idempotency_key</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>payload</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
@@ -17534,7 +18190,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>new_ticket</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -17544,7 +18200,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2030-01-15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -17554,17 +18210,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2030-01-15</t>
+          <t>true</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2030-01-15T08:00:00+03:00</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -17584,7 +18240,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>waiting_assignment</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -17594,17 +18250,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>\N</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>synthetic-1900-ticket-1</t>
+          <t>2030-01-15T08:00:00+03:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{"ticket_id":1}</t>
+          <t>2030-01-15T08:00:00+03:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -17629,164 +18285,60 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>brigade_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>worker_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>district_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>route_date</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>revision</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>unavailable_at</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>unavailable_until</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>last_location_id</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>current_ticket_id</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>current_destination_id</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>en_route_started_at</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>expected_available_at</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2030-01-15</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>\N</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1</t>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -17806,12 +18358,62 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>brigade_id</t>
+          <t>district_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>worker_id</t>
+          <t>route_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>revision</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>previous_revision</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>actor_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fingerprint</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>diff</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>is_current</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>id</t>
         </is>
       </c>
     </row>
@@ -17823,43 +18425,57 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>2030-01-15</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>\N</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>037af78dc92cfa511d01a1148b4013f72d2ef1c959523e157a79e73e128339a2</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2030-01-15T08:00:00+03:00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -17879,22 +18495,22 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>district_id</t>
+          <t>ticket_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>route_date</t>
+          <t>execution_cycle</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>revision</t>
+          <t>appliance_id</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>previous_revision</t>
+          <t>office_id</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -17904,35 +18520,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>actor_id</t>
+          <t>movement</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>fingerprint</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>diff</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>is_current</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
@@ -17946,7 +18547,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2030-01-15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -17956,7 +18557,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>\N</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -17966,35 +18567,20 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>consume</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>037af78dc92cfa511d01a1148b4013f72d2ef1c959523e157a79e73e128339a2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>2030-01-15T08:00:00+03:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -18077,113 +18663,6 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ticket_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>execution_cycle</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>appliance_id</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>office_id</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>event_id</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>movement</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>consume</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2030-01-15T08:00:00+03:00</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
           <t>worker_id</t>
         </is>
       </c>
